--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESTRIBO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESTRIBO.xlsx
@@ -453,7 +453,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -487,7 +495,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -508,7 +520,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -529,7 +545,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -550,7 +570,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -571,7 +595,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -594,7 +622,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t> </t>
+          <t>80</t>
         </is>
       </c>
     </row>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESTRIBO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESTRIBO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,11 +448,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -474,11 +464,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,11 +480,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,11 +500,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,11 +520,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,11 +540,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -595,11 +560,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -618,11 +578,6 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
     </row>
